--- a/research/traditional_assets/database/data/nigeria/nigeria_broadcasting.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_broadcasting.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0159</v>
+        <v>0.0915</v>
       </c>
       <c r="G2">
-        <v>-0.4081818181818182</v>
+        <v>0.01758064516129032</v>
       </c>
       <c r="H2">
-        <v>-0.4081818181818182</v>
+        <v>0.01758064516129032</v>
       </c>
       <c r="I2">
-        <v>-0.4081818181818182</v>
+        <v>-0.207258064516129</v>
       </c>
       <c r="J2">
-        <v>-0.4081818181818182</v>
+        <v>-0.207258064516129</v>
       </c>
       <c r="K2">
-        <v>-3.69</v>
+        <v>-3.44</v>
       </c>
       <c r="L2">
-        <v>-0.3354545454545454</v>
+        <v>-0.2774193548387097</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.266</v>
+        <v>0.391</v>
       </c>
       <c r="V2">
-        <v>0.06855670103092784</v>
+        <v>0.1092178770949721</v>
       </c>
       <c r="W2">
-        <v>-0.267391304347826</v>
+        <v>-0.3839285714285714</v>
       </c>
       <c r="X2">
-        <v>0.1176093768187902</v>
+        <v>0.192317231557449</v>
       </c>
       <c r="Y2">
-        <v>-0.3850006811666162</v>
+        <v>-0.5762458029860204</v>
       </c>
       <c r="Z2">
-        <v>0.6700371566059572</v>
+        <v>1.151346332404828</v>
       </c>
       <c r="AA2">
-        <v>-0.2734969848327953</v>
+        <v>-0.2386258124419684</v>
       </c>
       <c r="AB2">
-        <v>0.09715429711746715</v>
+        <v>0.1714843158452684</v>
       </c>
       <c r="AC2">
-        <v>-0.3706512819502624</v>
+        <v>-0.4101101282872368</v>
       </c>
       <c r="AD2">
-        <v>1.86</v>
+        <v>0.999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.86</v>
+        <v>0.999</v>
       </c>
       <c r="AG2">
-        <v>1.594</v>
+        <v>0.608</v>
       </c>
       <c r="AH2">
-        <v>0.3240418118466899</v>
+        <v>0.2181699060930334</v>
       </c>
       <c r="AI2">
-        <v>0.1669658886894076</v>
+        <v>0.1346542660735948</v>
       </c>
       <c r="AJ2">
-        <v>0.2911947387650712</v>
+        <v>0.1451766953199618</v>
       </c>
       <c r="AK2">
-        <v>0.1465881920176568</v>
+        <v>0.08651109846328971</v>
       </c>
       <c r="AL2">
         <v>0.096</v>
@@ -687,16 +687,16 @@
         <v>0.096</v>
       </c>
       <c r="AN2">
-        <v>-1.039106145251397</v>
+        <v>-2.034623217922607</v>
       </c>
       <c r="AO2">
-        <v>-46.77083333333334</v>
+        <v>-26.77083333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.8905027932960894</v>
+        <v>-1.238289205702648</v>
       </c>
       <c r="AQ2">
-        <v>-46.77083333333334</v>
+        <v>-26.77083333333333</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0159</v>
+        <v>0.0915</v>
       </c>
       <c r="G3">
-        <v>-0.4081818181818182</v>
+        <v>0.01758064516129032</v>
       </c>
       <c r="H3">
-        <v>-0.4081818181818182</v>
+        <v>0.01758064516129032</v>
       </c>
       <c r="I3">
-        <v>-0.4081818181818182</v>
+        <v>-0.207258064516129</v>
       </c>
       <c r="J3">
-        <v>-0.4081818181818182</v>
+        <v>-0.207258064516129</v>
       </c>
       <c r="K3">
-        <v>-3.69</v>
+        <v>-3.44</v>
       </c>
       <c r="L3">
-        <v>-0.3354545454545454</v>
+        <v>-0.2774193548387097</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.266</v>
+        <v>0.391</v>
       </c>
       <c r="V3">
-        <v>0.06855670103092784</v>
+        <v>0.1092178770949721</v>
       </c>
       <c r="W3">
-        <v>-0.267391304347826</v>
+        <v>-0.3839285714285714</v>
       </c>
       <c r="X3">
-        <v>0.1176093768187902</v>
+        <v>0.192317231557449</v>
       </c>
       <c r="Y3">
-        <v>-0.3850006811666162</v>
+        <v>-0.5762458029860204</v>
       </c>
       <c r="Z3">
-        <v>0.6700371566059572</v>
+        <v>1.151346332404828</v>
       </c>
       <c r="AA3">
-        <v>-0.2734969848327953</v>
+        <v>-0.2386258124419684</v>
       </c>
       <c r="AB3">
-        <v>0.09715429711746715</v>
+        <v>0.1714843158452684</v>
       </c>
       <c r="AC3">
-        <v>-0.3706512819502624</v>
+        <v>-0.4101101282872368</v>
       </c>
       <c r="AD3">
-        <v>1.86</v>
+        <v>0.999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.86</v>
+        <v>0.999</v>
       </c>
       <c r="AG3">
-        <v>1.594</v>
+        <v>0.608</v>
       </c>
       <c r="AH3">
-        <v>0.3240418118466899</v>
+        <v>0.2181699060930334</v>
       </c>
       <c r="AI3">
-        <v>0.1669658886894076</v>
+        <v>0.1346542660735948</v>
       </c>
       <c r="AJ3">
-        <v>0.2911947387650712</v>
+        <v>0.1451766953199618</v>
       </c>
       <c r="AK3">
-        <v>0.1465881920176568</v>
+        <v>0.08651109846328971</v>
       </c>
       <c r="AL3">
         <v>0.096</v>
@@ -815,16 +815,16 @@
         <v>0.096</v>
       </c>
       <c r="AN3">
-        <v>-1.039106145251397</v>
+        <v>-2.034623217922607</v>
       </c>
       <c r="AO3">
-        <v>-46.77083333333334</v>
+        <v>-26.77083333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.8905027932960894</v>
+        <v>-1.238289205702648</v>
       </c>
       <c r="AQ3">
-        <v>-46.77083333333334</v>
+        <v>-26.77083333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_broadcasting.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_broadcasting.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0915</v>
+        <v>0.009170000000000001</v>
       </c>
       <c r="G2">
-        <v>0.01758064516129032</v>
+        <v>0.01291390728476821</v>
       </c>
       <c r="H2">
-        <v>0.01758064516129032</v>
+        <v>0.01291390728476821</v>
       </c>
       <c r="I2">
-        <v>-0.207258064516129</v>
+        <v>-0.2334437086092715</v>
       </c>
       <c r="J2">
-        <v>-0.207258064516129</v>
+        <v>-0.2334437086092715</v>
       </c>
       <c r="K2">
-        <v>-3.44</v>
+        <v>-1.23</v>
       </c>
       <c r="L2">
-        <v>-0.2774193548387097</v>
+        <v>-0.2036423841059603</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.391</v>
+        <v>0.184</v>
       </c>
       <c r="V2">
-        <v>0.1092178770949721</v>
+        <v>0.02271604938271605</v>
       </c>
       <c r="W2">
-        <v>-0.3839285714285714</v>
+        <v>-0.2216216216216216</v>
       </c>
       <c r="X2">
-        <v>0.192317231557449</v>
+        <v>0.1469650920313469</v>
       </c>
       <c r="Y2">
-        <v>-0.5762458029860204</v>
+        <v>-0.3685867136529685</v>
       </c>
       <c r="Z2">
-        <v>1.151346332404828</v>
+        <v>1.003655699567963</v>
       </c>
       <c r="AA2">
-        <v>-0.2386258124419684</v>
+        <v>-0.2342971086739781</v>
       </c>
       <c r="AB2">
-        <v>0.1714843158452684</v>
+        <v>0.1454109762943226</v>
       </c>
       <c r="AC2">
-        <v>-0.4101101282872368</v>
+        <v>-0.3797080849683007</v>
       </c>
       <c r="AD2">
-        <v>0.999</v>
+        <v>0.248</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.999</v>
+        <v>0.248</v>
       </c>
       <c r="AG2">
-        <v>0.608</v>
+        <v>0.064</v>
       </c>
       <c r="AH2">
-        <v>0.2181699060930334</v>
+        <v>0.0297077144226162</v>
       </c>
       <c r="AI2">
-        <v>0.1346542660735948</v>
+        <v>0.113345521023766</v>
       </c>
       <c r="AJ2">
-        <v>0.1451766953199618</v>
+        <v>0.007839294463498285</v>
       </c>
       <c r="AK2">
-        <v>0.08651109846328971</v>
+        <v>0.03193612774451098</v>
       </c>
       <c r="AL2">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.096</v>
+        <v>-0.066</v>
       </c>
       <c r="AN2">
-        <v>-2.034623217922607</v>
-      </c>
-      <c r="AO2">
-        <v>-26.77083333333333</v>
+        <v>-0.5975903614457831</v>
       </c>
       <c r="AP2">
-        <v>-1.238289205702648</v>
+        <v>-0.1542168674698795</v>
       </c>
       <c r="AQ2">
-        <v>-26.77083333333333</v>
+        <v>21.36363636363636</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0915</v>
+        <v>0.009170000000000001</v>
       </c>
       <c r="G3">
-        <v>0.01758064516129032</v>
+        <v>0.01291390728476821</v>
       </c>
       <c r="H3">
-        <v>0.01758064516129032</v>
+        <v>0.01291390728476821</v>
       </c>
       <c r="I3">
-        <v>-0.207258064516129</v>
+        <v>-0.2334437086092715</v>
       </c>
       <c r="J3">
-        <v>-0.207258064516129</v>
+        <v>-0.2334437086092715</v>
       </c>
       <c r="K3">
-        <v>-3.44</v>
+        <v>-1.23</v>
       </c>
       <c r="L3">
-        <v>-0.2774193548387097</v>
+        <v>-0.2036423841059603</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +755,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.391</v>
+        <v>0.184</v>
       </c>
       <c r="V3">
-        <v>0.1092178770949721</v>
+        <v>0.02271604938271605</v>
       </c>
       <c r="W3">
-        <v>-0.3839285714285714</v>
+        <v>-0.2216216216216216</v>
       </c>
       <c r="X3">
-        <v>0.192317231557449</v>
+        <v>0.1469650920313469</v>
       </c>
       <c r="Y3">
-        <v>-0.5762458029860204</v>
+        <v>-0.3685867136529685</v>
       </c>
       <c r="Z3">
-        <v>1.151346332404828</v>
+        <v>1.003655699567963</v>
       </c>
       <c r="AA3">
-        <v>-0.2386258124419684</v>
+        <v>-0.2342971086739781</v>
       </c>
       <c r="AB3">
-        <v>0.1714843158452684</v>
+        <v>0.1454109762943226</v>
       </c>
       <c r="AC3">
-        <v>-0.4101101282872368</v>
+        <v>-0.3797080849683007</v>
       </c>
       <c r="AD3">
-        <v>0.999</v>
+        <v>0.248</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.999</v>
+        <v>0.248</v>
       </c>
       <c r="AG3">
-        <v>0.608</v>
+        <v>0.064</v>
       </c>
       <c r="AH3">
-        <v>0.2181699060930334</v>
+        <v>0.0297077144226162</v>
       </c>
       <c r="AI3">
-        <v>0.1346542660735948</v>
+        <v>0.113345521023766</v>
       </c>
       <c r="AJ3">
-        <v>0.1451766953199618</v>
+        <v>0.007839294463498285</v>
       </c>
       <c r="AK3">
-        <v>0.08651109846328971</v>
+        <v>0.03193612774451098</v>
       </c>
       <c r="AL3">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.096</v>
+        <v>-0.066</v>
       </c>
       <c r="AN3">
-        <v>-2.034623217922607</v>
-      </c>
-      <c r="AO3">
-        <v>-26.77083333333333</v>
+        <v>-0.5975903614457831</v>
       </c>
       <c r="AP3">
-        <v>-1.238289205702648</v>
+        <v>-0.1542168674698795</v>
       </c>
       <c r="AQ3">
-        <v>-26.77083333333333</v>
+        <v>21.36363636363636</v>
       </c>
     </row>
   </sheetData>
